--- a/india_compliance/gst_india/data/test_gstr2b_export_golden.xlsx
+++ b/india_compliance/gst_india/data/test_gstr2b_export_golden.xlsx
@@ -11206,6 +11206,21 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>Nov'19</t>
@@ -11582,6 +11597,21 @@
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="K8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="46" t="n">
+        <v>0</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -12884,6 +12914,21 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>Nov'19</t>
@@ -13290,6 +13335,21 @@
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="N8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="46" t="n">
+        <v>0</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>

--- a/india_compliance/gst_india/data/test_gstr2b_export_golden.xlsx
+++ b/india_compliance/gst_india/data/test_gstr2b_export_golden.xlsx
@@ -9714,7 +9714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="3"/>
@@ -9935,6 +9935,276 @@
         </is>
       </c>
       <c r="N7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>27AABCE2207R1Z5</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GSTN Mixed Eligibility</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ISD Invoice</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>S9001</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>03/03/2016</t>
+        </is>
+      </c>
+      <c r="H8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="46" t="n">
+        <v>200</v>
+      </c>
+      <c r="J8" s="46" t="n">
+        <v>200</v>
+      </c>
+      <c r="K8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Feb'20</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>02/03/2020</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>27AABCE2207R1Z5</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GSTN Mixed Eligibility</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ISD Invoice</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>S9002</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>03/03/2016</t>
+        </is>
+      </c>
+      <c r="H9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="J9" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="K9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Feb'20</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>02/03/2020</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>27AABCE2207R1Z5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GSTN Mixed Eligibility</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ISD Credit Note</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>S9003</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>03/03/2016</t>
+        </is>
+      </c>
+      <c r="H10" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="46" t="n">
+        <v>50</v>
+      </c>
+      <c r="J10" s="46" t="n">
+        <v>50</v>
+      </c>
+      <c r="K10" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Feb'20</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>02/03/2020</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>29AABCE2207R1Z5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GSTN Same Series</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ISD Invoice</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>S9010</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>03/03/2016</t>
+        </is>
+      </c>
+      <c r="H11" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="46" t="n">
+        <v>300</v>
+      </c>
+      <c r="J11" s="46" t="n">
+        <v>300</v>
+      </c>
+      <c r="K11" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Feb'20</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>02/03/2020</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>29AABCE2207R1Z5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GSTN Same Series</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ISD Credit Note</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>S9010</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>04/03/2016</t>
+        </is>
+      </c>
+      <c r="H12" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="J12" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="K12" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Feb'20</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>02/03/2020</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
